--- a/data_lake/macro/China/Caixin PMI.xlsx
+++ b/data_lake/macro/China/Caixin PMI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C58866D-DDF4-4CC9-8F7F-DF1E5F0571FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82D7E8-6860-4DC0-AE08-A458A031CD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
   </bookViews>
   <sheets>
     <sheet name="CAIXINPMI" sheetId="1" r:id="rId1"/>
@@ -5744,6 +5744,9 @@
       <c r="A249" s="6">
         <v>45992</v>
       </c>
+      <c r="B249" s="2">
+        <v>46022</v>
+      </c>
       <c r="C249" s="3">
         <v>0.40625</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>46023</v>
       </c>
       <c r="B250" s="2">
-        <v>46022</v>
+        <v>46052</v>
       </c>
       <c r="C250" s="3">
         <v>0.40625</v>

--- a/data_lake/macro/China/Caixin PMI.xlsx
+++ b/data_lake/macro/China/Caixin PMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82D7E8-6860-4DC0-AE08-A458A031CD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D596B125-0217-437C-96DD-C7FACE875DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="14">
   <si>
     <t>Actual</t>
   </si>
@@ -79,6 +79,9 @@
   <si>
     <t>CAIXINPMI</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTC+8</t>
   </si>
 </sst>
 </file>
@@ -494,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACEB860-D90B-474B-9AD2-3F1BDA064BA5}">
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G256"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="1" bestFit="1" customWidth="1"/>
@@ -5870,6 +5873,52 @@
       </c>
       <c r="G254" s="4">
         <v>52.2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A255" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C255" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E255" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="F255" s="4">
+        <v>51.9</v>
+      </c>
+      <c r="G255" s="4">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A256" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46237</v>
+      </c>
+      <c r="C256" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E256" s="4">
+        <v>50.9</v>
+      </c>
+      <c r="F256" s="4">
+        <v>51.9</v>
+      </c>
+      <c r="G256" s="4">
+        <v>51.7</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/macro/China/Caixin PMI.xlsx
+++ b/data_lake/macro/China/Caixin PMI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D596B125-0217-437C-96DD-C7FACE875DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C84119D-AA45-4936-AB58-2A8BC423E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="14">
   <si>
     <t>Actual</t>
   </si>
@@ -497,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACEB860-D90B-474B-9AD2-3F1BDA064BA5}">
-  <dimension ref="A1:G256"/>
+  <dimension ref="A1:G257"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="1" bestFit="1" customWidth="1"/>
@@ -5919,6 +5919,23 @@
       </c>
       <c r="G256" s="4">
         <v>51.7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A257" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C257" s="3">
+        <v>0.40625</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G257" s="4">
+        <v>50.9</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/macro/China/Caixin PMI.xlsx
+++ b/data_lake/macro/China/Caixin PMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/China/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C84119D-AA45-4936-AB58-2A8BC423E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1B5815-9776-D941-9173-B73927BCD57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="19340" windowHeight="20800" activeTab="1" xr2:uid="{1B6B37A9-D6A6-4771-8E64-93DD2EFDCD72}"/>
   </bookViews>
   <sheets>
     <sheet name="CAIXINPMI" sheetId="1" r:id="rId1"/>
@@ -77,11 +77,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAIXINPMI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>UTC+8</t>
   </si>
   <si>
-    <t>UTC+8</t>
+    <t>CAIXINPMI</t>
   </si>
 </sst>
 </file>
@@ -89,12 +88,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +132,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -151,22 +157,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -174,18 +181,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -201,9 +210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -241,7 +250,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -347,7 +356,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,7 +498,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -498,20 +507,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACEB860-D90B-474B-9AD2-3F1BDA064BA5}">
   <dimension ref="A1:G257"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="5"/>
+    <col min="7" max="7" width="10.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="8" t="s">
@@ -533,8 +542,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2">
         <v>38473</v>
       </c>
       <c r="B2" s="2">
@@ -550,8 +559,8 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2">
         <v>38504</v>
       </c>
       <c r="B3" s="2">
@@ -570,8 +579,8 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
         <v>38534</v>
       </c>
       <c r="B4" s="2">
@@ -590,8 +599,8 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:7">
+      <c r="A5" s="2">
         <v>38565</v>
       </c>
       <c r="B5" s="2">
@@ -610,8 +619,8 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:7">
+      <c r="A6" s="2">
         <v>38596</v>
       </c>
       <c r="B6" s="2">
@@ -630,8 +639,8 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:7">
+      <c r="A7" s="2">
         <v>38626</v>
       </c>
       <c r="B7" s="2">
@@ -650,8 +659,8 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:7">
+      <c r="A8" s="2">
         <v>38657</v>
       </c>
       <c r="B8" s="2">
@@ -670,8 +679,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+    <row r="9" spans="1:7">
+      <c r="A9" s="2">
         <v>38687</v>
       </c>
       <c r="B9" s="2">
@@ -690,8 +699,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+    <row r="10" spans="1:7">
+      <c r="A10" s="2">
         <v>38718</v>
       </c>
       <c r="B10" s="2">
@@ -710,8 +719,8 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
+    <row r="11" spans="1:7">
+      <c r="A11" s="2">
         <v>38749</v>
       </c>
       <c r="B11" s="2">
@@ -730,8 +739,8 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+    <row r="12" spans="1:7">
+      <c r="A12" s="2">
         <v>38777</v>
       </c>
       <c r="B12" s="2">
@@ -750,8 +759,8 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:7">
+      <c r="A13" s="2">
         <v>38808</v>
       </c>
       <c r="B13" s="2">
@@ -770,8 +779,8 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:7">
+      <c r="A14" s="2">
         <v>38838</v>
       </c>
       <c r="B14" s="2">
@@ -790,8 +799,8 @@
         <v>54.4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
+    <row r="15" spans="1:7">
+      <c r="A15" s="2">
         <v>38869</v>
       </c>
       <c r="B15" s="2">
@@ -810,8 +819,8 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+    <row r="16" spans="1:7">
+      <c r="A16" s="2">
         <v>38899</v>
       </c>
       <c r="B16" s="2">
@@ -830,8 +839,8 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
+    <row r="17" spans="1:7">
+      <c r="A17" s="2">
         <v>38930</v>
       </c>
       <c r="B17" s="2">
@@ -850,8 +859,8 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:7">
+      <c r="A18" s="2">
         <v>38961</v>
       </c>
       <c r="B18" s="2">
@@ -870,8 +879,8 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6">
+    <row r="19" spans="1:7">
+      <c r="A19" s="2">
         <v>38991</v>
       </c>
       <c r="B19" s="2">
@@ -890,8 +899,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
+    <row r="20" spans="1:7">
+      <c r="A20" s="2">
         <v>39022</v>
       </c>
       <c r="B20" s="2">
@@ -910,8 +919,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
+    <row r="21" spans="1:7">
+      <c r="A21" s="2">
         <v>39052</v>
       </c>
       <c r="B21" s="2">
@@ -930,8 +939,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
+    <row r="22" spans="1:7">
+      <c r="A22" s="2">
         <v>39083</v>
       </c>
       <c r="B22" s="2">
@@ -950,8 +959,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
         <v>39114</v>
       </c>
       <c r="B23" s="2">
@@ -970,8 +979,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
         <v>39142</v>
       </c>
       <c r="B24" s="2">
@@ -990,8 +999,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
         <v>39173</v>
       </c>
       <c r="B25" s="2">
@@ -1010,8 +1019,8 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
         <v>39203</v>
       </c>
       <c r="B26" s="2">
@@ -1030,8 +1039,8 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
         <v>39234</v>
       </c>
       <c r="B27" s="2">
@@ -1050,8 +1059,8 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
         <v>39264</v>
       </c>
       <c r="B28" s="2">
@@ -1070,8 +1079,8 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
         <v>39295</v>
       </c>
       <c r="B29" s="2">
@@ -1090,8 +1099,8 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
         <v>39326</v>
       </c>
       <c r="B30" s="2">
@@ -1110,8 +1119,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="6">
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
         <v>39356</v>
       </c>
       <c r="B31" s="2">
@@ -1130,8 +1139,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="6">
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
         <v>39387</v>
       </c>
       <c r="B32" s="2">
@@ -1150,8 +1159,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="6">
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
         <v>39417</v>
       </c>
       <c r="B33" s="2">
@@ -1170,8 +1179,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="6">
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
         <v>39448</v>
       </c>
       <c r="B34" s="2">
@@ -1190,8 +1199,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="6">
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
         <v>39479</v>
       </c>
       <c r="B35" s="2">
@@ -1210,8 +1219,8 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="6">
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
         <v>39508</v>
       </c>
       <c r="B36" s="2">
@@ -1230,8 +1239,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="6">
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
         <v>39539</v>
       </c>
       <c r="B37" s="2">
@@ -1250,8 +1259,8 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="6">
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
         <v>39569</v>
       </c>
       <c r="B38" s="2">
@@ -1270,8 +1279,8 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="6">
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
         <v>39600</v>
       </c>
       <c r="B39" s="2">
@@ -1290,8 +1299,8 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="6">
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
         <v>39630</v>
       </c>
       <c r="B40" s="2">
@@ -1310,8 +1319,8 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
         <v>39661</v>
       </c>
       <c r="B41" s="2">
@@ -1330,8 +1339,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
         <v>39692</v>
       </c>
       <c r="B42" s="2">
@@ -1350,8 +1359,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
         <v>39722</v>
       </c>
       <c r="B43" s="2">
@@ -1370,8 +1379,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
         <v>39753</v>
       </c>
       <c r="B44" s="2">
@@ -1390,8 +1399,8 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="6">
+    <row r="45" spans="1:7">
+      <c r="A45" s="2">
         <v>39783</v>
       </c>
       <c r="B45" s="2">
@@ -1410,8 +1419,8 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="6">
+    <row r="46" spans="1:7">
+      <c r="A46" s="2">
         <v>39814</v>
       </c>
       <c r="B46" s="2">
@@ -1430,8 +1439,8 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="6">
+    <row r="47" spans="1:7">
+      <c r="A47" s="2">
         <v>39845</v>
       </c>
       <c r="B47" s="2">
@@ -1450,8 +1459,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="6">
+    <row r="48" spans="1:7">
+      <c r="A48" s="2">
         <v>39873</v>
       </c>
       <c r="B48" s="2">
@@ -1470,8 +1479,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="6">
+    <row r="49" spans="1:7">
+      <c r="A49" s="2">
         <v>39904</v>
       </c>
       <c r="B49" s="2">
@@ -1490,8 +1499,8 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="6">
+    <row r="50" spans="1:7">
+      <c r="A50" s="2">
         <v>39934</v>
       </c>
       <c r="B50" s="2">
@@ -1510,8 +1519,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="6">
+    <row r="51" spans="1:7">
+      <c r="A51" s="2">
         <v>39965</v>
       </c>
       <c r="B51" s="2">
@@ -1530,8 +1539,8 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="6">
+    <row r="52" spans="1:7">
+      <c r="A52" s="2">
         <v>39995</v>
       </c>
       <c r="B52" s="2">
@@ -1550,8 +1559,8 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="6">
+    <row r="53" spans="1:7">
+      <c r="A53" s="2">
         <v>40026</v>
       </c>
       <c r="B53" s="2">
@@ -1570,8 +1579,8 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
+    <row r="54" spans="1:7">
+      <c r="A54" s="2">
         <v>40057</v>
       </c>
       <c r="B54" s="2">
@@ -1590,8 +1599,8 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
+    <row r="55" spans="1:7">
+      <c r="A55" s="2">
         <v>40087</v>
       </c>
       <c r="B55" s="2">
@@ -1610,8 +1619,8 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="6">
+    <row r="56" spans="1:7">
+      <c r="A56" s="2">
         <v>40118</v>
       </c>
       <c r="B56" s="2">
@@ -1630,8 +1639,8 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="6">
+    <row r="57" spans="1:7">
+      <c r="A57" s="2">
         <v>40148</v>
       </c>
       <c r="B57" s="2">
@@ -1650,8 +1659,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="6">
+    <row r="58" spans="1:7">
+      <c r="A58" s="2">
         <v>40179</v>
       </c>
       <c r="B58" s="2">
@@ -1670,8 +1679,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="6">
+    <row r="59" spans="1:7">
+      <c r="A59" s="2">
         <v>40210</v>
       </c>
       <c r="B59" s="2">
@@ -1690,8 +1699,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="6">
+    <row r="60" spans="1:7">
+      <c r="A60" s="2">
         <v>40238</v>
       </c>
       <c r="B60" s="2">
@@ -1710,8 +1719,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="6">
+    <row r="61" spans="1:7">
+      <c r="A61" s="2">
         <v>40269</v>
       </c>
       <c r="B61" s="2">
@@ -1730,8 +1739,8 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="6">
+    <row r="62" spans="1:7">
+      <c r="A62" s="2">
         <v>40299</v>
       </c>
       <c r="B62" s="2">
@@ -1750,8 +1759,8 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="6">
+    <row r="63" spans="1:7">
+      <c r="A63" s="2">
         <v>40330</v>
       </c>
       <c r="B63" s="2">
@@ -1770,8 +1779,8 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="6">
+    <row r="64" spans="1:7">
+      <c r="A64" s="2">
         <v>40360</v>
       </c>
       <c r="B64" s="2">
@@ -1790,8 +1799,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="6">
+    <row r="65" spans="1:7">
+      <c r="A65" s="2">
         <v>40391</v>
       </c>
       <c r="B65" s="2">
@@ -1810,8 +1819,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="6">
+    <row r="66" spans="1:7">
+      <c r="A66" s="2">
         <v>40422</v>
       </c>
       <c r="B66" s="2">
@@ -1830,8 +1839,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="6">
+    <row r="67" spans="1:7">
+      <c r="A67" s="2">
         <v>40452</v>
       </c>
       <c r="B67" s="2">
@@ -1850,8 +1859,8 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="6">
+    <row r="68" spans="1:7">
+      <c r="A68" s="2">
         <v>40483</v>
       </c>
       <c r="B68" s="2">
@@ -1870,8 +1879,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
+    <row r="69" spans="1:7">
+      <c r="A69" s="2">
         <v>40513</v>
       </c>
       <c r="B69" s="2">
@@ -1890,8 +1899,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="6">
+    <row r="70" spans="1:7">
+      <c r="A70" s="2">
         <v>40544</v>
       </c>
       <c r="B70" s="2">
@@ -1910,8 +1919,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="6">
+    <row r="71" spans="1:7">
+      <c r="A71" s="2">
         <v>40575</v>
       </c>
       <c r="B71" s="2">
@@ -1930,8 +1939,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="6">
+    <row r="72" spans="1:7">
+      <c r="A72" s="2">
         <v>40603</v>
       </c>
       <c r="B72" s="2">
@@ -1950,8 +1959,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="6">
+    <row r="73" spans="1:7">
+      <c r="A73" s="2">
         <v>40634</v>
       </c>
       <c r="B73" s="2">
@@ -1970,8 +1979,8 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="6">
+    <row r="74" spans="1:7">
+      <c r="A74" s="2">
         <v>40664</v>
       </c>
       <c r="B74" s="2">
@@ -1990,8 +1999,8 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="6">
+    <row r="75" spans="1:7">
+      <c r="A75" s="2">
         <v>40695</v>
       </c>
       <c r="B75" s="2">
@@ -2010,8 +2019,8 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="6">
+    <row r="76" spans="1:7">
+      <c r="A76" s="2">
         <v>40725</v>
       </c>
       <c r="B76" s="2">
@@ -2030,8 +2039,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="6">
+    <row r="77" spans="1:7">
+      <c r="A77" s="2">
         <v>40756</v>
       </c>
       <c r="B77" s="2">
@@ -2050,8 +2059,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="6">
+    <row r="78" spans="1:7">
+      <c r="A78" s="2">
         <v>40787</v>
       </c>
       <c r="B78" s="2">
@@ -2070,8 +2079,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="6">
+    <row r="79" spans="1:7">
+      <c r="A79" s="2">
         <v>40817</v>
       </c>
       <c r="B79" s="2">
@@ -2090,8 +2099,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="6">
+    <row r="80" spans="1:7">
+      <c r="A80" s="2">
         <v>40848</v>
       </c>
       <c r="B80" s="2">
@@ -2110,8 +2119,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="6">
+    <row r="81" spans="1:7">
+      <c r="A81" s="2">
         <v>40878</v>
       </c>
       <c r="B81" s="2">
@@ -2130,8 +2139,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="6">
+    <row r="82" spans="1:7">
+      <c r="A82" s="2">
         <v>40909</v>
       </c>
       <c r="B82" s="2">
@@ -2150,8 +2159,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="6">
+    <row r="83" spans="1:7">
+      <c r="A83" s="2">
         <v>40940</v>
       </c>
       <c r="B83" s="2">
@@ -2170,8 +2179,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="6">
+    <row r="84" spans="1:7">
+      <c r="A84" s="2">
         <v>40969</v>
       </c>
       <c r="B84" s="2">
@@ -2190,8 +2199,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="6">
+    <row r="85" spans="1:7">
+      <c r="A85" s="2">
         <v>41000</v>
       </c>
       <c r="B85" s="2">
@@ -2210,8 +2219,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="6">
+    <row r="86" spans="1:7">
+      <c r="A86" s="2">
         <v>41030</v>
       </c>
       <c r="B86" s="2">
@@ -2230,8 +2239,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="6">
+    <row r="87" spans="1:7">
+      <c r="A87" s="2">
         <v>41061</v>
       </c>
       <c r="B87" s="2">
@@ -2250,8 +2259,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="6">
+    <row r="88" spans="1:7">
+      <c r="A88" s="2">
         <v>41091</v>
       </c>
       <c r="B88" s="2">
@@ -2270,8 +2279,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="6">
+    <row r="89" spans="1:7">
+      <c r="A89" s="2">
         <v>41122</v>
       </c>
       <c r="B89" s="2">
@@ -2290,8 +2299,8 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="6">
+    <row r="90" spans="1:7">
+      <c r="A90" s="2">
         <v>41153</v>
       </c>
       <c r="B90" s="2">
@@ -2310,8 +2319,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="6">
+    <row r="91" spans="1:7">
+      <c r="A91" s="2">
         <v>41183</v>
       </c>
       <c r="B91" s="2">
@@ -2330,8 +2339,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="6">
+    <row r="92" spans="1:7">
+      <c r="A92" s="2">
         <v>41214</v>
       </c>
       <c r="B92" s="2">
@@ -2350,8 +2359,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="6">
+    <row r="93" spans="1:7">
+      <c r="A93" s="2">
         <v>41244</v>
       </c>
       <c r="B93" s="2">
@@ -2370,8 +2379,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="6">
+    <row r="94" spans="1:7">
+      <c r="A94" s="2">
         <v>41275</v>
       </c>
       <c r="B94" s="2">
@@ -2390,8 +2399,8 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="6">
+    <row r="95" spans="1:7">
+      <c r="A95" s="2">
         <v>41306</v>
       </c>
       <c r="B95" s="2">
@@ -2410,8 +2419,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="6">
+    <row r="96" spans="1:7">
+      <c r="A96" s="2">
         <v>41334</v>
       </c>
       <c r="B96" s="2">
@@ -2430,8 +2439,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="6">
+    <row r="97" spans="1:7">
+      <c r="A97" s="2">
         <v>41365</v>
       </c>
       <c r="B97" s="2">
@@ -2450,8 +2459,8 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="6">
+    <row r="98" spans="1:7">
+      <c r="A98" s="2">
         <v>41395</v>
       </c>
       <c r="B98" s="2">
@@ -2470,8 +2479,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="6">
+    <row r="99" spans="1:7">
+      <c r="A99" s="2">
         <v>41426</v>
       </c>
       <c r="B99" s="2">
@@ -2490,8 +2499,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="6">
+    <row r="100" spans="1:7">
+      <c r="A100" s="2">
         <v>41456</v>
       </c>
       <c r="B100" s="2">
@@ -2510,8 +2519,8 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="6">
+    <row r="101" spans="1:7">
+      <c r="A101" s="2">
         <v>41487</v>
       </c>
       <c r="B101" s="2">
@@ -2530,8 +2539,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="6">
+    <row r="102" spans="1:7">
+      <c r="A102" s="2">
         <v>41518</v>
       </c>
       <c r="B102" s="2">
@@ -2550,8 +2559,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="6">
+    <row r="103" spans="1:7">
+      <c r="A103" s="2">
         <v>41548</v>
       </c>
       <c r="B103" s="2">
@@ -2570,8 +2579,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="6">
+    <row r="104" spans="1:7">
+      <c r="A104" s="2">
         <v>41579</v>
       </c>
       <c r="B104" s="2">
@@ -2590,8 +2599,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="6">
+    <row r="105" spans="1:7">
+      <c r="A105" s="2">
         <v>41609</v>
       </c>
       <c r="B105" s="2">
@@ -2610,8 +2619,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="6">
+    <row r="106" spans="1:7">
+      <c r="A106" s="2">
         <v>41640</v>
       </c>
       <c r="B106" s="2">
@@ -2630,8 +2639,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="6">
+    <row r="107" spans="1:7">
+      <c r="A107" s="2">
         <v>41671</v>
       </c>
       <c r="B107" s="2">
@@ -2650,8 +2659,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="6">
+    <row r="108" spans="1:7">
+      <c r="A108" s="2">
         <v>41699</v>
       </c>
       <c r="B108" s="2">
@@ -2670,8 +2679,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="6">
+    <row r="109" spans="1:7">
+      <c r="A109" s="2">
         <v>41730</v>
       </c>
       <c r="B109" s="2">
@@ -2690,8 +2699,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="6">
+    <row r="110" spans="1:7">
+      <c r="A110" s="2">
         <v>41760</v>
       </c>
       <c r="B110" s="2">
@@ -2710,8 +2719,8 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="6">
+    <row r="111" spans="1:7">
+      <c r="A111" s="2">
         <v>41791</v>
       </c>
       <c r="B111" s="2">
@@ -2730,8 +2739,8 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="6">
+    <row r="112" spans="1:7">
+      <c r="A112" s="2">
         <v>41821</v>
       </c>
       <c r="B112" s="2">
@@ -2750,8 +2759,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="6">
+    <row r="113" spans="1:7">
+      <c r="A113" s="2">
         <v>41852</v>
       </c>
       <c r="B113" s="2">
@@ -2770,8 +2779,8 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="6">
+    <row r="114" spans="1:7">
+      <c r="A114" s="2">
         <v>41883</v>
       </c>
       <c r="B114" s="2">
@@ -2790,8 +2799,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="6">
+    <row r="115" spans="1:7">
+      <c r="A115" s="2">
         <v>41913</v>
       </c>
       <c r="B115" s="2">
@@ -2810,8 +2819,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="6">
+    <row r="116" spans="1:7">
+      <c r="A116" s="2">
         <v>41944</v>
       </c>
       <c r="B116" s="2">
@@ -2830,8 +2839,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="6">
+    <row r="117" spans="1:7">
+      <c r="A117" s="2">
         <v>41974</v>
       </c>
       <c r="B117" s="2">
@@ -2850,8 +2859,8 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="6">
+    <row r="118" spans="1:7">
+      <c r="A118" s="2">
         <v>42005</v>
       </c>
       <c r="B118" s="2">
@@ -2870,8 +2879,8 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="6">
+    <row r="119" spans="1:7">
+      <c r="A119" s="2">
         <v>42036</v>
       </c>
       <c r="B119" s="2">
@@ -2890,8 +2899,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="6">
+    <row r="120" spans="1:7">
+      <c r="A120" s="2">
         <v>42064</v>
       </c>
       <c r="B120" s="2">
@@ -2910,8 +2919,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="6">
+    <row r="121" spans="1:7">
+      <c r="A121" s="2">
         <v>42095</v>
       </c>
       <c r="B121" s="2">
@@ -2930,8 +2939,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="6">
+    <row r="122" spans="1:7">
+      <c r="A122" s="2">
         <v>42125</v>
       </c>
       <c r="B122" s="2">
@@ -2950,8 +2959,8 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="6">
+    <row r="123" spans="1:7">
+      <c r="A123" s="2">
         <v>42156</v>
       </c>
       <c r="B123" s="2">
@@ -2970,8 +2979,8 @@
         <v>47.8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="6">
+    <row r="124" spans="1:7">
+      <c r="A124" s="2">
         <v>42186</v>
       </c>
       <c r="B124" s="2">
@@ -2990,8 +2999,8 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="6">
+    <row r="125" spans="1:7">
+      <c r="A125" s="2">
         <v>42217</v>
       </c>
       <c r="B125" s="2">
@@ -3010,8 +3019,8 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="6">
+    <row r="126" spans="1:7">
+      <c r="A126" s="2">
         <v>42248</v>
       </c>
       <c r="B126" s="2">
@@ -3030,8 +3039,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="6">
+    <row r="127" spans="1:7">
+      <c r="A127" s="2">
         <v>42278</v>
       </c>
       <c r="B127" s="2">
@@ -3050,8 +3059,8 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="6">
+    <row r="128" spans="1:7">
+      <c r="A128" s="2">
         <v>42309</v>
       </c>
       <c r="B128" s="2">
@@ -3070,8 +3079,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="6">
+    <row r="129" spans="1:7">
+      <c r="A129" s="2">
         <v>42339</v>
       </c>
       <c r="B129" s="2">
@@ -3090,8 +3099,8 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="6">
+    <row r="130" spans="1:7">
+      <c r="A130" s="2">
         <v>42370</v>
       </c>
       <c r="B130" s="2">
@@ -3110,8 +3119,8 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="6">
+    <row r="131" spans="1:7">
+      <c r="A131" s="2">
         <v>42401</v>
       </c>
       <c r="B131" s="2">
@@ -3130,8 +3139,8 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="6">
+    <row r="132" spans="1:7">
+      <c r="A132" s="2">
         <v>42430</v>
       </c>
       <c r="B132" s="2">
@@ -3150,8 +3159,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="6">
+    <row r="133" spans="1:7">
+      <c r="A133" s="2">
         <v>42461</v>
       </c>
       <c r="B133" s="2">
@@ -3170,8 +3179,8 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="6">
+    <row r="134" spans="1:7">
+      <c r="A134" s="2">
         <v>42491</v>
       </c>
       <c r="B134" s="2">
@@ -3190,8 +3199,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="6">
+    <row r="135" spans="1:7">
+      <c r="A135" s="2">
         <v>42522</v>
       </c>
       <c r="B135" s="2">
@@ -3210,8 +3219,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="6">
+    <row r="136" spans="1:7">
+      <c r="A136" s="2">
         <v>42552</v>
       </c>
       <c r="B136" s="2">
@@ -3230,8 +3239,8 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="6">
+    <row r="137" spans="1:7">
+      <c r="A137" s="2">
         <v>42583</v>
       </c>
       <c r="B137" s="2">
@@ -3250,8 +3259,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="6">
+    <row r="138" spans="1:7">
+      <c r="A138" s="2">
         <v>42614</v>
       </c>
       <c r="B138" s="2">
@@ -3270,8 +3279,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="6">
+    <row r="139" spans="1:7">
+      <c r="A139" s="2">
         <v>42644</v>
       </c>
       <c r="B139" s="2">
@@ -3290,8 +3299,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="6">
+    <row r="140" spans="1:7">
+      <c r="A140" s="2">
         <v>42675</v>
       </c>
       <c r="B140" s="2">
@@ -3310,8 +3319,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="6">
+    <row r="141" spans="1:7">
+      <c r="A141" s="2">
         <v>42705</v>
       </c>
       <c r="B141" s="2">
@@ -3330,8 +3339,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="6">
+    <row r="142" spans="1:7">
+      <c r="A142" s="2">
         <v>42736</v>
       </c>
       <c r="B142" s="2">
@@ -3350,8 +3359,8 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="6">
+    <row r="143" spans="1:7">
+      <c r="A143" s="2">
         <v>42767</v>
       </c>
       <c r="B143" s="2">
@@ -3370,8 +3379,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="6">
+    <row r="144" spans="1:7">
+      <c r="A144" s="2">
         <v>42795</v>
       </c>
       <c r="B144" s="2">
@@ -3390,8 +3399,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="6">
+    <row r="145" spans="1:7">
+      <c r="A145" s="2">
         <v>42826</v>
       </c>
       <c r="B145" s="2">
@@ -3410,8 +3419,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="6">
+    <row r="146" spans="1:7">
+      <c r="A146" s="2">
         <v>42856</v>
       </c>
       <c r="B146" s="2">
@@ -3430,8 +3439,8 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="6">
+    <row r="147" spans="1:7">
+      <c r="A147" s="2">
         <v>42887</v>
       </c>
       <c r="B147" s="2">
@@ -3450,8 +3459,8 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="6">
+    <row r="148" spans="1:7">
+      <c r="A148" s="2">
         <v>42917</v>
       </c>
       <c r="B148" s="2">
@@ -3470,8 +3479,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="6">
+    <row r="149" spans="1:7">
+      <c r="A149" s="2">
         <v>42948</v>
       </c>
       <c r="B149" s="2">
@@ -3490,8 +3499,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="6">
+    <row r="150" spans="1:7">
+      <c r="A150" s="2">
         <v>42979</v>
       </c>
       <c r="B150" s="2">
@@ -3510,8 +3519,8 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="6">
+    <row r="151" spans="1:7">
+      <c r="A151" s="2">
         <v>43009</v>
       </c>
       <c r="B151" s="2">
@@ -3530,8 +3539,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="6">
+    <row r="152" spans="1:7">
+      <c r="A152" s="2">
         <v>43040</v>
       </c>
       <c r="B152" s="2">
@@ -3550,8 +3559,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="6">
+    <row r="153" spans="1:7">
+      <c r="A153" s="2">
         <v>43070</v>
       </c>
       <c r="B153" s="2">
@@ -3570,8 +3579,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="6">
+    <row r="154" spans="1:7">
+      <c r="A154" s="2">
         <v>43101</v>
       </c>
       <c r="B154" s="2">
@@ -3590,8 +3599,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="6">
+    <row r="155" spans="1:7">
+      <c r="A155" s="2">
         <v>43132</v>
       </c>
       <c r="B155" s="2">
@@ -3610,8 +3619,8 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="6">
+    <row r="156" spans="1:7">
+      <c r="A156" s="2">
         <v>43160</v>
       </c>
       <c r="B156" s="2">
@@ -3630,8 +3639,8 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="6">
+    <row r="157" spans="1:7">
+      <c r="A157" s="2">
         <v>43191</v>
       </c>
       <c r="B157" s="2">
@@ -3653,8 +3662,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="6">
+    <row r="158" spans="1:7">
+      <c r="A158" s="2">
         <v>43221</v>
       </c>
       <c r="B158" s="2">
@@ -3676,8 +3685,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="6">
+    <row r="159" spans="1:7">
+      <c r="A159" s="2">
         <v>43252</v>
       </c>
       <c r="B159" s="2">
@@ -3699,8 +3708,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="6">
+    <row r="160" spans="1:7">
+      <c r="A160" s="2">
         <v>43282</v>
       </c>
       <c r="B160" s="2">
@@ -3722,8 +3731,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="6">
+    <row r="161" spans="1:7">
+      <c r="A161" s="2">
         <v>43313</v>
       </c>
       <c r="B161" s="2">
@@ -3745,8 +3754,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="6">
+    <row r="162" spans="1:7">
+      <c r="A162" s="2">
         <v>43344</v>
       </c>
       <c r="B162" s="2">
@@ -3768,8 +3777,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="6">
+    <row r="163" spans="1:7">
+      <c r="A163" s="2">
         <v>43374</v>
       </c>
       <c r="B163" s="2">
@@ -3791,8 +3800,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="6">
+    <row r="164" spans="1:7">
+      <c r="A164" s="2">
         <v>43405</v>
       </c>
       <c r="B164" s="2">
@@ -3814,8 +3823,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="6">
+    <row r="165" spans="1:7">
+      <c r="A165" s="2">
         <v>43435</v>
       </c>
       <c r="B165" s="2">
@@ -3837,8 +3846,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="6">
+    <row r="166" spans="1:7">
+      <c r="A166" s="2">
         <v>43466</v>
       </c>
       <c r="B166" s="2">
@@ -3860,8 +3869,8 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="6">
+    <row r="167" spans="1:7">
+      <c r="A167" s="2">
         <v>43497</v>
       </c>
       <c r="B167" s="2">
@@ -3883,8 +3892,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="6">
+    <row r="168" spans="1:7">
+      <c r="A168" s="2">
         <v>43525</v>
       </c>
       <c r="B168" s="2">
@@ -3906,8 +3915,8 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="6">
+    <row r="169" spans="1:7">
+      <c r="A169" s="2">
         <v>43556</v>
       </c>
       <c r="B169" s="2">
@@ -3929,8 +3938,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="6">
+    <row r="170" spans="1:7">
+      <c r="A170" s="2">
         <v>43586</v>
       </c>
       <c r="B170" s="2">
@@ -3952,8 +3961,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="6">
+    <row r="171" spans="1:7">
+      <c r="A171" s="2">
         <v>43617</v>
       </c>
       <c r="B171" s="2">
@@ -3975,8 +3984,8 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="6">
+    <row r="172" spans="1:7">
+      <c r="A172" s="2">
         <v>43647</v>
       </c>
       <c r="B172" s="2">
@@ -3998,8 +4007,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="6">
+    <row r="173" spans="1:7">
+      <c r="A173" s="2">
         <v>43678</v>
       </c>
       <c r="B173" s="2">
@@ -4021,8 +4030,8 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="6">
+    <row r="174" spans="1:7">
+      <c r="A174" s="2">
         <v>43709</v>
       </c>
       <c r="B174" s="2">
@@ -4044,8 +4053,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="6">
+    <row r="175" spans="1:7">
+      <c r="A175" s="2">
         <v>43739</v>
       </c>
       <c r="B175" s="2">
@@ -4067,8 +4076,8 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" s="6">
+    <row r="176" spans="1:7">
+      <c r="A176" s="2">
         <v>43770</v>
       </c>
       <c r="B176" s="2">
@@ -4090,8 +4099,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="6">
+    <row r="177" spans="1:7">
+      <c r="A177" s="2">
         <v>43800</v>
       </c>
       <c r="B177" s="2">
@@ -4113,8 +4122,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="6">
+    <row r="178" spans="1:7">
+      <c r="A178" s="2">
         <v>43831</v>
       </c>
       <c r="B178" s="2">
@@ -4136,8 +4145,8 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="6">
+    <row r="179" spans="1:7">
+      <c r="A179" s="2">
         <v>43862</v>
       </c>
       <c r="B179" s="2">
@@ -4159,8 +4168,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="6">
+    <row r="180" spans="1:7">
+      <c r="A180" s="2">
         <v>43891</v>
       </c>
       <c r="B180" s="2">
@@ -4182,8 +4191,8 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="6">
+    <row r="181" spans="1:7">
+      <c r="A181" s="2">
         <v>43922</v>
       </c>
       <c r="B181" s="2">
@@ -4205,8 +4214,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="6">
+    <row r="182" spans="1:7">
+      <c r="A182" s="2">
         <v>43952</v>
       </c>
       <c r="B182" s="2">
@@ -4228,8 +4237,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="6">
+    <row r="183" spans="1:7">
+      <c r="A183" s="2">
         <v>43983</v>
       </c>
       <c r="B183" s="2">
@@ -4251,8 +4260,8 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="6">
+    <row r="184" spans="1:7">
+      <c r="A184" s="2">
         <v>44013</v>
       </c>
       <c r="B184" s="2">
@@ -4274,8 +4283,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="6">
+    <row r="185" spans="1:7">
+      <c r="A185" s="2">
         <v>44044</v>
       </c>
       <c r="B185" s="2">
@@ -4297,8 +4306,8 @@
         <v>52.8</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="6">
+    <row r="186" spans="1:7">
+      <c r="A186" s="2">
         <v>44075</v>
       </c>
       <c r="B186" s="2">
@@ -4320,8 +4329,8 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="6">
+    <row r="187" spans="1:7">
+      <c r="A187" s="2">
         <v>44105</v>
       </c>
       <c r="B187" s="2">
@@ -4343,8 +4352,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="6">
+    <row r="188" spans="1:7">
+      <c r="A188" s="2">
         <v>44136</v>
       </c>
       <c r="B188" s="2">
@@ -4366,8 +4375,8 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="6">
+    <row r="189" spans="1:7">
+      <c r="A189" s="2">
         <v>44166</v>
       </c>
       <c r="B189" s="2">
@@ -4389,8 +4398,8 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="6">
+    <row r="190" spans="1:7">
+      <c r="A190" s="2">
         <v>44197</v>
       </c>
       <c r="B190" s="2">
@@ -4412,8 +4421,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="6">
+    <row r="191" spans="1:7">
+      <c r="A191" s="2">
         <v>44228</v>
       </c>
       <c r="B191" s="2">
@@ -4435,8 +4444,8 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="6">
+    <row r="192" spans="1:7">
+      <c r="A192" s="2">
         <v>44256</v>
       </c>
       <c r="B192" s="2">
@@ -4458,8 +4467,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" s="6">
+    <row r="193" spans="1:7">
+      <c r="A193" s="2">
         <v>44287</v>
       </c>
       <c r="B193" s="2">
@@ -4481,8 +4490,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="6">
+    <row r="194" spans="1:7">
+      <c r="A194" s="2">
         <v>44317</v>
       </c>
       <c r="B194" s="2">
@@ -4504,8 +4513,8 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="6">
+    <row r="195" spans="1:7">
+      <c r="A195" s="2">
         <v>44348</v>
       </c>
       <c r="B195" s="2">
@@ -4527,8 +4536,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="6">
+    <row r="196" spans="1:7">
+      <c r="A196" s="2">
         <v>44378</v>
       </c>
       <c r="B196" s="2">
@@ -4550,8 +4559,8 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="6">
+    <row r="197" spans="1:7">
+      <c r="A197" s="2">
         <v>44409</v>
       </c>
       <c r="B197" s="2">
@@ -4573,8 +4582,8 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="6">
+    <row r="198" spans="1:7">
+      <c r="A198" s="2">
         <v>44440</v>
       </c>
       <c r="B198" s="2">
@@ -4596,8 +4605,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="6">
+    <row r="199" spans="1:7">
+      <c r="A199" s="2">
         <v>44470</v>
       </c>
       <c r="B199" s="2">
@@ -4619,8 +4628,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="6">
+    <row r="200" spans="1:7">
+      <c r="A200" s="2">
         <v>44501</v>
       </c>
       <c r="B200" s="2">
@@ -4642,8 +4651,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="6">
+    <row r="201" spans="1:7">
+      <c r="A201" s="2">
         <v>44531</v>
       </c>
       <c r="B201" s="2">
@@ -4665,8 +4674,8 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="6">
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
         <v>44562</v>
       </c>
       <c r="B202" s="2">
@@ -4688,8 +4697,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="6">
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
         <v>44593</v>
       </c>
       <c r="B203" s="2">
@@ -4711,8 +4720,8 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="6">
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
         <v>44621</v>
       </c>
       <c r="B204" s="2">
@@ -4734,8 +4743,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="6">
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
         <v>44652</v>
       </c>
       <c r="B205" s="2">
@@ -4757,8 +4766,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="6">
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
         <v>44682</v>
       </c>
       <c r="B206" s="2">
@@ -4780,8 +4789,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="6">
+    <row r="207" spans="1:7">
+      <c r="A207" s="2">
         <v>44713</v>
       </c>
       <c r="B207" s="2">
@@ -4803,8 +4812,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="6">
+    <row r="208" spans="1:7">
+      <c r="A208" s="2">
         <v>44743</v>
       </c>
       <c r="B208" s="2">
@@ -4826,8 +4835,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="6">
+    <row r="209" spans="1:7">
+      <c r="A209" s="2">
         <v>44774</v>
       </c>
       <c r="B209" s="2">
@@ -4849,8 +4858,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" s="6">
+    <row r="210" spans="1:7">
+      <c r="A210" s="2">
         <v>44805</v>
       </c>
       <c r="B210" s="2">
@@ -4872,8 +4881,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="6">
+    <row r="211" spans="1:7">
+      <c r="A211" s="2">
         <v>44835</v>
       </c>
       <c r="B211" s="2">
@@ -4895,8 +4904,8 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="6">
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
         <v>44866</v>
       </c>
       <c r="B212" s="2">
@@ -4918,8 +4927,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="6">
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
         <v>44896</v>
       </c>
       <c r="B213" s="2">
@@ -4941,8 +4950,8 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="6">
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
         <v>44927</v>
       </c>
       <c r="B214" s="2">
@@ -4964,8 +4973,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="6">
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
         <v>44958</v>
       </c>
       <c r="B215" s="2">
@@ -4987,8 +4996,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="6">
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
         <v>44986</v>
       </c>
       <c r="B216" s="2">
@@ -5010,8 +5019,8 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="6">
+    <row r="217" spans="1:7">
+      <c r="A217" s="2">
         <v>45017</v>
       </c>
       <c r="B217" s="2">
@@ -5033,8 +5042,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="6">
+    <row r="218" spans="1:7">
+      <c r="A218" s="2">
         <v>45047</v>
       </c>
       <c r="B218" s="2">
@@ -5056,8 +5065,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" s="6">
+    <row r="219" spans="1:7">
+      <c r="A219" s="2">
         <v>45078</v>
       </c>
       <c r="B219" s="2">
@@ -5079,8 +5088,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" s="6">
+    <row r="220" spans="1:7">
+      <c r="A220" s="2">
         <v>45108</v>
       </c>
       <c r="B220" s="2">
@@ -5102,8 +5111,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" s="6">
+    <row r="221" spans="1:7">
+      <c r="A221" s="2">
         <v>45139</v>
       </c>
       <c r="B221" s="2">
@@ -5125,8 +5134,8 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" s="6">
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
         <v>45170</v>
       </c>
       <c r="B222" s="2">
@@ -5148,8 +5157,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" s="6">
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
         <v>45200</v>
       </c>
       <c r="B223" s="2">
@@ -5171,8 +5180,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" s="6">
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
         <v>45231</v>
       </c>
       <c r="B224" s="2">
@@ -5194,8 +5203,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" s="6">
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
         <v>45261</v>
       </c>
       <c r="B225" s="2">
@@ -5217,8 +5226,8 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="6">
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
         <v>45292</v>
       </c>
       <c r="B226" s="2">
@@ -5240,8 +5249,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" s="6">
+    <row r="227" spans="1:7">
+      <c r="A227" s="2">
         <v>45323</v>
       </c>
       <c r="B227" s="2">
@@ -5263,8 +5272,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" s="6">
+    <row r="228" spans="1:7">
+      <c r="A228" s="2">
         <v>45352</v>
       </c>
       <c r="B228" s="2">
@@ -5286,8 +5295,8 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" s="6">
+    <row r="229" spans="1:7">
+      <c r="A229" s="2">
         <v>45383</v>
       </c>
       <c r="B229" s="2">
@@ -5309,8 +5318,8 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A230" s="6">
+    <row r="230" spans="1:7">
+      <c r="A230" s="2">
         <v>45413</v>
       </c>
       <c r="B230" s="2">
@@ -5332,8 +5341,8 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A231" s="6">
+    <row r="231" spans="1:7">
+      <c r="A231" s="2">
         <v>45444</v>
       </c>
       <c r="B231" s="2">
@@ -5355,8 +5364,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" s="6">
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
         <v>45474</v>
       </c>
       <c r="B232" s="2">
@@ -5378,8 +5387,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" s="6">
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
         <v>45505</v>
       </c>
       <c r="B233" s="2">
@@ -5401,8 +5410,8 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" s="6">
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
         <v>45536</v>
       </c>
       <c r="B234" s="2">
@@ -5424,8 +5433,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A235" s="6">
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
         <v>45566</v>
       </c>
       <c r="B235" s="2">
@@ -5447,8 +5456,8 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" s="6">
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
         <v>45597</v>
       </c>
       <c r="B236" s="2">
@@ -5470,8 +5479,8 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" s="6">
+    <row r="237" spans="1:7">
+      <c r="A237" s="2">
         <v>45627</v>
       </c>
       <c r="B237" s="2">
@@ -5493,8 +5502,8 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A238" s="6">
+    <row r="238" spans="1:7">
+      <c r="A238" s="2">
         <v>45658</v>
       </c>
       <c r="B238" s="2">
@@ -5516,8 +5525,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" s="6">
+    <row r="239" spans="1:7">
+      <c r="A239" s="2">
         <v>45689</v>
       </c>
       <c r="B239" s="2">
@@ -5539,8 +5548,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A240" s="6">
+    <row r="240" spans="1:7">
+      <c r="A240" s="2">
         <v>45717</v>
       </c>
       <c r="B240" s="2">
@@ -5562,8 +5571,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" s="6">
+    <row r="241" spans="1:7">
+      <c r="A241" s="2">
         <v>45748</v>
       </c>
       <c r="B241" s="2">
@@ -5585,8 +5594,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" s="6">
+    <row r="242" spans="1:7">
+      <c r="A242" s="2">
         <v>45778</v>
       </c>
       <c r="B242" s="2">
@@ -5608,8 +5617,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="6">
+    <row r="243" spans="1:7">
+      <c r="A243" s="2">
         <v>45809</v>
       </c>
       <c r="B243" s="2">
@@ -5631,8 +5640,8 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="6">
+    <row r="244" spans="1:7">
+      <c r="A244" s="2">
         <v>45839</v>
       </c>
       <c r="B244" s="2">
@@ -5654,8 +5663,8 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="6">
+    <row r="245" spans="1:7">
+      <c r="A245" s="2">
         <v>45870</v>
       </c>
       <c r="B245" s="2">
@@ -5677,8 +5686,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="6">
+    <row r="246" spans="1:7">
+      <c r="A246" s="2">
         <v>45901</v>
       </c>
       <c r="B246" s="2">
@@ -5700,8 +5709,8 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="6">
+    <row r="247" spans="1:7">
+      <c r="A247" s="2">
         <v>45931</v>
       </c>
       <c r="B247" s="2">
@@ -5720,8 +5729,8 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="6">
+    <row r="248" spans="1:7">
+      <c r="A248" s="2">
         <v>45962</v>
       </c>
       <c r="B248" s="2">
@@ -5743,8 +5752,8 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="6">
+    <row r="249" spans="1:7">
+      <c r="A249" s="2">
         <v>45992</v>
       </c>
       <c r="B249" s="2">
@@ -5763,8 +5772,8 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="6">
+    <row r="250" spans="1:7">
+      <c r="A250" s="2">
         <v>46023</v>
       </c>
       <c r="B250" s="2">
@@ -5786,8 +5795,8 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="6">
+    <row r="251" spans="1:7">
+      <c r="A251" s="2">
         <v>46054</v>
       </c>
       <c r="B251" s="2">
@@ -5806,8 +5815,8 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" s="6">
+    <row r="252" spans="1:7">
+      <c r="A252" s="2">
         <v>46082</v>
       </c>
       <c r="B252" s="2">
@@ -5829,8 +5838,8 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="6">
+    <row r="253" spans="1:7">
+      <c r="A253" s="2">
         <v>46113</v>
       </c>
       <c r="B253" s="2">
@@ -5852,8 +5861,8 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" s="6">
+    <row r="254" spans="1:7">
+      <c r="A254" s="2">
         <v>46143</v>
       </c>
       <c r="B254" s="2">
@@ -5875,8 +5884,8 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" s="6">
+    <row r="255" spans="1:7">
+      <c r="A255" s="2">
         <v>46174</v>
       </c>
       <c r="B255" s="2">
@@ -5886,7 +5895,7 @@
         <v>0.40625</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E255" s="4">
         <v>51.7</v>
@@ -5898,8 +5907,8 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="6">
+    <row r="256" spans="1:7">
+      <c r="A256" s="2">
         <v>46204</v>
       </c>
       <c r="B256" s="2">
@@ -5909,7 +5918,7 @@
         <v>0.40625</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E256" s="4">
         <v>50.9</v>
@@ -5921,8 +5930,8 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" s="6">
+    <row r="257" spans="1:7">
+      <c r="A257" s="2">
         <v>46235</v>
       </c>
       <c r="B257" s="2">
@@ -5932,7 +5941,7 @@
         <v>0.40625</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G257" s="4">
         <v>50.9</v>
@@ -5950,13 +5959,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFCE244B-5C7D-4EC8-82AD-EB7D80430834}">
   <dimension ref="B2:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4">
       <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
@@ -5964,19 +5973,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4">
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{0844527F-6A66-A747-A173-6519BC875F4F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>